--- a/resultados/amapora/erros_varredura.xlsx
+++ b/resultados/amapora/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -472,7 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30 09:34:12</t>
+          <t>2026-07-30 09:36:14</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/31/pss-enfermeiro/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/32/processo-seletivo-auxiliar-e-tecnico-em-enfermagem/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30 09:36:14</t>
+          <t>2026-07-30 09:40:28</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/32/processo-seletivo-auxiliar-e-tecnico-em-enfermagem/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/33/processo-seletivo-itai-instituto-de-tecnologia-aplicada-e-inovacao/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-30 09:38:26</t>
+          <t>2026-07-30 09:45:50</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/32/processo-seletivo-auxiliar-e-tecnico-em-enfermagem/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/35/pss-odontologo-2025/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-30 09:40:28</t>
+          <t>2026-07-30 09:51:08</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/33/processo-seletivo-itai-instituto-de-tecnologia-aplicada-e-inovacao/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/37/pss-professor-02-2025/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -584,7 +584,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30 09:43:48</t>
+          <t>2026-07-30 09:56:26</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/33/processo-seletivo-itai-instituto-de-tecnologia-aplicada-e-inovacao/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/38/pss-medico-2025/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30 09:45:50</t>
+          <t>2026-07-30 10:01:44</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/35/pss-odontologo-2025/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/39/pss-saude-2025/</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30 09:49:06</t>
+          <t>2026-07-30 10:05:46</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/35/pss-odontologo-2025/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/40/pss-diversos-2025/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30 09:51:08</t>
+          <t>2026-07-30 10:09:52</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/37/pss-professor-02-2025/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/41/eleicoes/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30 09:54:24</t>
+          <t>2026-07-30 10:13:58</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/37/pss-professor-02-2025/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/42/concurso-publico-n-542025/</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30 09:56:26</t>
+          <t>2026-07-30 10:18:08</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/38/pss-medico-2025/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/43/concurso-emprego-publico-2025/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30 09:59:44</t>
+          <t>2026-07-30 10:23:24</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/38/pss-medico-2025/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/46/pss-02-2026-saude-e-assistencia-social/</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30 10:01:44</t>
+          <t>2026-07-30 10:27:32</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/39/pss-saude-2025/</t>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2024/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30 10:03:45</t>
+          <t>2026-07-30 10:31:32</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/39/pss-saude-2025/</t>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2023/</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30 10:05:46</t>
+          <t>2026-07-30 10:36:53</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/40/pss-diversos-2025/</t>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2022/</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30 10:07:52</t>
+          <t>2026-07-30 10:42:14</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/40/pss-diversos-2025/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/15/assistencia-social/</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30 10:09:52</t>
+          <t>2026-07-30 10:47:33</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/41/eleicoes/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/7/educacao/</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30 10:11:58</t>
+          <t>2026-07-30 10:52:53</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/41/eleicoes/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/23/consulta-publica-para-a-elaboracao-do-plano-anual-de-aplicacao-dos-recursos/</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30 10:13:58</t>
+          <t>2026-07-30 10:58:21</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/42/concurso-publico-n-542025/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/21/eleicao-para-conselheiro-tutelar-2023/</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30 10:16:07</t>
+          <t>2026-07-30 11:03:50</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/42/concurso-publico-n-542025/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/20/consulta-publica-lei-paulo-gustavo-2023-amapora-pr/</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-30 10:18:08</t>
+          <t>2026-07-30 11:09:06</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/43/concurso-emprego-publico-2025/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/17/convite-setembro-amarelo/</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-30 10:21:24</t>
+          <t>2026-07-30 11:14:27</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/43/concurso-emprego-publico-2025/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/16/assistencia-social-de-amapora/</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-30 10:23:24</t>
+          <t>2026-07-30 11:18:29</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/46/pss-02-2026-saude-e-assistencia-social/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/15/cadastro-unico-/</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-30 10:25:31</t>
+          <t>2026-07-30 11:22:42</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/concurso/categoria/46/pss-02-2026-saude-e-assistencia-social/</t>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/page/2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-30 10:27:32</t>
+          <t>2026-07-30 11:28:06</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2024/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/6/</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-30 10:29:31</t>
+          <t>2026-07-30 11:32:20</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2024/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/5/</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-30 10:31:32</t>
+          <t>2026-07-30 11:37:42</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2023/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/4/</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30 10:34:52</t>
+          <t>2026-07-30 11:42:57</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2023/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/3/</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30 10:36:53</t>
+          <t>2026-07-30 11:47:09</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2022/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30 10:40:13</t>
+          <t>2026-07-30 11:52:26</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2022/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30 10:42:14</t>
+          <t>2026-07-30 11:57:44</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/categoria/15/assistencia-social/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30 10:45:32</t>
+          <t>2026-07-30 12:01:53</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/categoria/15/assistencia-social/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-30 10:47:33</t>
+          <t>2026-07-30 12:05:56</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/categoria/7/educacao/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-30 10:50:52</t>
+          <t>2026-07-30 12:09:58</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/categoria/7/educacao/</t>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-30 10:52:53</t>
+          <t>2026-07-30 12:15:24</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/23/consulta-publica-para-a-elaboracao-do-plano-anual-de-aplicacao-dos-recursos/</t>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30 10:56:20</t>
+          <t>2026-07-30 12:20:47</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/23/consulta-publica-para-a-elaboracao-do-plano-anual-de-aplicacao-dos-recursos/</t>
+          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-30 10:58:21</t>
+          <t>2026-07-30 12:24:47</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/21/eleicao-para-conselheiro-tutelar-2023/</t>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30 11:01:49</t>
+          <t>2026-07-30 12:30:18</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/21/eleicao-para-conselheiro-tutelar-2023/</t>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/download/1/</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30 11:03:50</t>
+          <t>2026-07-30 12:35:44</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/20/consulta-publica-lei-paulo-gustavo-2023-amapora-pr/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-30 11:07:05</t>
+          <t>2026-07-30 15:23:58</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/20/consulta-publica-lei-paulo-gustavo-2023-amapora-pr/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30 11:09:06</t>
+          <t>2026-07-30 15:25:59</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/17/convite-setembro-amarelo/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-30 11:12:26</t>
+          <t>2026-07-30 15:28:04</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/17/convite-setembro-amarelo/</t>
+          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-30 11:14:27</t>
+          <t>2026-07-30 15:30:06</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/16/assistencia-social-de-amapora/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30 11:16:29</t>
+          <t>2026-07-30 15:33:24</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/16/assistencia-social-de-amapora/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-30 11:18:29</t>
+          <t>2026-07-30 15:35:26</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/15/cadastro-unico-/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-30 11:20:42</t>
+          <t>2026-07-30 15:38:47</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/15/cadastro-unico-/</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-30 11:22:42</t>
+          <t>2026-07-30 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/categoria/page/2</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30 11:26:05</t>
+          <t>2026-07-30 15:44:12</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/noticia/categoria/page/2</t>
+          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28:06</t>
+          <t>2026-07-30 15:46:13</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/6/</t>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30 11:30:19</t>
+          <t>2026-07-30 15:49:32</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/6/</t>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-30 11:32:20</t>
+          <t>2026-07-30 15:51:33</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/5/</t>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-30 11:35:42</t>
+          <t>2026-07-30 15:54:55</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/5/</t>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-30 11:37:42</t>
+          <t>2026-07-30 15:56:56</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/4/</t>
+          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-30 11:40:57</t>
+          <t>2026-07-30 16:00:13</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/4/</t>
+          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-30 11:42:57</t>
+          <t>2026-07-30 16:02:14</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/3/</t>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-30 11:45:09</t>
+          <t>2026-07-30 16:05:35</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/3/</t>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-30 11:47:09</t>
+          <t>2026-07-30 16:07:37</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/download/1/</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-30 11:50:26</t>
+          <t>2026-07-30 16:11:02</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/download/1/</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-30 11:52:26</t>
+          <t>2026-07-30 16:12:06</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/31/pss-enfermeiro/</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-30 11:55:44</t>
+          <t>2026-07-30 16:14:54</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/31/pss-enfermeiro/</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-30 11:57:44</t>
+          <t>2026-07-30 16:16:56</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/32/processo-seletivo-auxiliar-e-tecnico-em-enfermagem/</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-30 11:59:53</t>
+          <t>2026-07-30 16:19:08</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/32/processo-seletivo-auxiliar-e-tecnico-em-enfermagem/</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-30 12:01:53</t>
+          <t>2026-07-30 16:21:10</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/33/processo-seletivo-itai-instituto-de-tecnologia-aplicada-e-inovacao/</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-30 12:03:55</t>
+          <t>2026-07-30 16:24:30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/33/processo-seletivo-itai-instituto-de-tecnologia-aplicada-e-inovacao/</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-30 12:05:56</t>
+          <t>2026-07-30 16:26:31</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/35/pss-odontologo-2025/</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-30 12:07:57</t>
+          <t>2026-07-30 16:29:50</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/35/pss-odontologo-2025/</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-30 12:09:58</t>
+          <t>2026-07-30 16:31:51</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/37/pss-professor-02-2025/</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-30 12:13:24</t>
+          <t>2026-07-30 16:35:06</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/37/pss-professor-02-2025/</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-30 12:15:24</t>
+          <t>2026-07-30 16:37:07</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/38/pss-medico-2025/</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-30 12:18:46</t>
+          <t>2026-07-30 16:40:24</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/38/pss-medico-2025/</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-30 12:20:47</t>
+          <t>2026-07-30 16:42:26</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/39/pss-saude-2025/</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-30 12:22:47</t>
+          <t>2026-07-30 16:44:28</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/39/pss-saude-2025/</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-30 12:24:47</t>
+          <t>2026-07-30 16:46:30</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/40/pss-diversos-2025/</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-30 12:28:17</t>
+          <t>2026-07-30 17:02:53</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/40/pss-diversos-2025/</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-30 12:30:18</t>
+          <t>2026-07-30 17:04:55</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/download/1/</t>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/41/eleicoes/</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-30 12:33:44</t>
+          <t>2026-07-30 17:08:13</t>
         </is>
       </c>
     </row>
@@ -2556,23 +2556,1647 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/41/eleicoes/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:10:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/42/concurso-publico-n-542025/</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/42/concurso-publico-n-542025/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/43/concurso-emprego-publico-2025/</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:24:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/43/concurso-emprego-publico-2025/</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:25:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/46/pss-02-2026-saude-e-assistencia-social/</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:37:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/concurso/categoria/46/pss-02-2026-saude-e-assistencia-social/</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:37:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2024/</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:39:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2024/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2023/</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:45:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2023/</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:46:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2022/</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:50:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/auxilio-brasil/2022/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:50:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/15/assistencia-social/</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:55:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/15/assistencia-social/</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:56:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/7/educacao/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:59:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/7/educacao/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:01:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/23/consulta-publica-para-a-elaboracao-do-plano-anual-de-aplicacao-dos-recursos/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/23/consulta-publica-para-a-elaboracao-do-plano-anual-de-aplicacao-dos-recursos/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:06:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/21/eleicao-para-conselheiro-tutelar-2023/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/21/eleicao-para-conselheiro-tutelar-2023/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:24:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/20/consulta-publica-lei-paulo-gustavo-2023-amapora-pr/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:27:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/20/consulta-publica-lei-paulo-gustavo-2023-amapora-pr/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:29:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/17/convite-setembro-amarelo/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:31:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/17/convite-setembro-amarelo/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:33:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/16/assistencia-social-de-amapora/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:36:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/16/assistencia-social-de-amapora/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:38:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/15/cadastro-unico-/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:41:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/15/cadastro-unico-/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:43:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/page/2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:46:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/noticia/categoria/page/2</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:48:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/6/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:51:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/6/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:54:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/5/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:57:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/5/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:59:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/4/</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:01:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/4/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:03:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/3/</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:06:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/3/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:08:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:12:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/2/</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:14:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/itr/download/1/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:19:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/86/p-styletext-alignjustifystrongcontratacao-de-empresa-de-organizacao-geral-de-eventos-para-organizacao-da-festa-do-trabalhador-a-ser-realizada-nos-dias-22-de-maio-e-23-de-maio-de-2026-no-municipio-de-amapora-prstrongp/</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:25:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:28:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/licitacao/detalhe/87/p-styletext-alignjustifyspan-stylecolorblackstrongcontratacao-de-empresa-especializada-para-o-fornecimento-montagem-e-desmontagem-de-palco-e-tendas-e-operacao-de-palco-tendas-sistema-de-som-iluminacao-cenica-painel-de-led-e-banheiros-quimicos-destinadas-a-realizacao-do-evento/</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/licitacao/categoria/24/dispensa-de-licitacao-nova-lei-141332021/</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:35:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:37:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/chamado-anonimo/</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:39:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:41:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/ouvidoria/change-email/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:44:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:45:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/guia-da-cidade/cadastro-empresa/</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:47:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:50:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/sub-pagina/9/</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:52:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>https://www.amapora.pr.gov.br/pagina/5/informativos/download/1/</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-30 12:35:44</t>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:55:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>amapora</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.amapora.pr.gov.br/pagina/5/informativos/download/1/</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-30 19:57:38</t>
         </is>
       </c>
     </row>
